--- a/www/terminologies/ValueSet-jdv-modalite-sortie-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-modalite-sortie-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141839</t>
+    <t>20260220142104</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:39+01:00</t>
+    <t>2026-02-20T14:21:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-modalite-sortie-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-modalite-sortie-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142104</t>
+    <t>20260311144904</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:04+01:00</t>
+    <t>2026-03-11T14:49:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-modalite-sortie-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-modalite-sortie-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144904</t>
+    <t>20260420150251</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:04+01:00</t>
+    <t>2026-04-20T15:02:51+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -122,6 +122,15 @@
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
   </si>
   <si>
+    <t>160849004</t>
+  </si>
+  <si>
+    <t>retour au domicile</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
     <t>109</t>
   </si>
   <si>
@@ -140,16 +149,7 @@
     <t>Etablissement d'hébergement pour personnes âgées dépendantes</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R66-CategorieEtablissement/FHIR/TRE-R66-CategorieEtablissement</t>
-  </si>
-  <si>
-    <t>160849004</t>
-  </si>
-  <si>
-    <t>retour au domicile</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r397-categorie-entite-geographique-exercice</t>
   </si>
 </sst>
 </file>
@@ -467,6 +467,52 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -484,26 +530,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
@@ -519,52 +565,6 @@
         <v>33</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>41</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B4" t="s" s="2">
         <v>44</v>
       </c>
     </row>

--- a/www/terminologies/ValueSet-jdv-modalite-sortie-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-modalite-sortie-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150251</t>
+    <t>20260619134043</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:51+01:00</t>
+    <t>2026-06-19T13:40:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-modalite-sortie-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-modalite-sortie-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260619134043</t>
+    <t>20260420150251</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:40:43+01:00</t>
+    <t>2026-04-20T15:02:51+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-modalite-sortie-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-modalite-sortie-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260619134043</t>
+    <t>20260716085852</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:40:43+01:00</t>
+    <t>2026-07-16T08:58:52+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
